--- a/artfynd/A 57321-2024 artfynd.xlsx
+++ b/artfynd/A 57321-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3117,6 +3117,123 @@
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>121853328</v>
+      </c>
+      <c r="B24" t="n">
+        <v>95660</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>53</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Gölbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>534995</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6671743</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Gysinge Skog naturvärdesbedömning.</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>gammal barrblandskog med tjock mossmatta</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>tallåga över bäck</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 57321-2024 artfynd.xlsx
+++ b/artfynd/A 57321-2024 artfynd.xlsx
@@ -3122,7 +3122,7 @@
         <v>121853328</v>
       </c>
       <c r="B24" t="n">
-        <v>95660</v>
+        <v>95678</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>

--- a/artfynd/A 57321-2024 artfynd.xlsx
+++ b/artfynd/A 57321-2024 artfynd.xlsx
@@ -3122,7 +3122,7 @@
         <v>121853328</v>
       </c>
       <c r="B24" t="n">
-        <v>95678</v>
+        <v>95680</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>

--- a/artfynd/A 57321-2024 artfynd.xlsx
+++ b/artfynd/A 57321-2024 artfynd.xlsx
@@ -3122,7 +3122,7 @@
         <v>121853328</v>
       </c>
       <c r="B24" t="n">
-        <v>95680</v>
+        <v>95687</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>

--- a/artfynd/A 57321-2024 artfynd.xlsx
+++ b/artfynd/A 57321-2024 artfynd.xlsx
@@ -3122,7 +3122,7 @@
         <v>121853328</v>
       </c>
       <c r="B24" t="n">
-        <v>95687</v>
+        <v>95696</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>

--- a/artfynd/A 57321-2024 artfynd.xlsx
+++ b/artfynd/A 57321-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3234,6 +3234,327 @@
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>125830789</v>
+      </c>
+      <c r="B25" t="n">
+        <v>103755</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Gölbäcken - Knapptjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>534901</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6671688</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson, Åke Persson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>125830768</v>
+      </c>
+      <c r="B26" t="n">
+        <v>100506</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Gölbäcken - Knapptjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>534901</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6671688</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson, Åke Persson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>125830803</v>
+      </c>
+      <c r="B27" t="n">
+        <v>101410</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Gölbäcken - Knapptjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>534901</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6671688</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson, Åke Persson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 57321-2024 artfynd.xlsx
+++ b/artfynd/A 57321-2024 artfynd.xlsx
@@ -3239,7 +3239,7 @@
         <v>125830789</v>
       </c>
       <c r="B25" t="n">
-        <v>103755</v>
+        <v>103762</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>125830768</v>
       </c>
       <c r="B26" t="n">
-        <v>100506</v>
+        <v>100513</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         <v>125830803</v>
       </c>
       <c r="B27" t="n">
-        <v>101410</v>
+        <v>101417</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 57321-2024 artfynd.xlsx
+++ b/artfynd/A 57321-2024 artfynd.xlsx
@@ -3239,7 +3239,7 @@
         <v>125830789</v>
       </c>
       <c r="B25" t="n">
-        <v>103762</v>
+        <v>103763</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>125830768</v>
       </c>
       <c r="B26" t="n">
-        <v>100513</v>
+        <v>100514</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         <v>125830803</v>
       </c>
       <c r="B27" t="n">
-        <v>101417</v>
+        <v>101418</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 57321-2024 artfynd.xlsx
+++ b/artfynd/A 57321-2024 artfynd.xlsx
@@ -3239,7 +3239,7 @@
         <v>125830789</v>
       </c>
       <c r="B25" t="n">
-        <v>103763</v>
+        <v>103765</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>125830768</v>
       </c>
       <c r="B26" t="n">
-        <v>100514</v>
+        <v>100516</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         <v>125830803</v>
       </c>
       <c r="B27" t="n">
-        <v>101418</v>
+        <v>101420</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 57321-2024 artfynd.xlsx
+++ b/artfynd/A 57321-2024 artfynd.xlsx
@@ -3239,7 +3239,7 @@
         <v>125830789</v>
       </c>
       <c r="B25" t="n">
-        <v>103765</v>
+        <v>103769</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>125830768</v>
       </c>
       <c r="B26" t="n">
-        <v>100516</v>
+        <v>100520</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         <v>125830803</v>
       </c>
       <c r="B27" t="n">
-        <v>101420</v>
+        <v>101424</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 57321-2024 artfynd.xlsx
+++ b/artfynd/A 57321-2024 artfynd.xlsx
@@ -3239,7 +3239,7 @@
         <v>125830789</v>
       </c>
       <c r="B25" t="n">
-        <v>103769</v>
+        <v>103770</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>125830768</v>
       </c>
       <c r="B26" t="n">
-        <v>100520</v>
+        <v>100521</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         <v>125830803</v>
       </c>
       <c r="B27" t="n">
-        <v>101424</v>
+        <v>101425</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 57321-2024 artfynd.xlsx
+++ b/artfynd/A 57321-2024 artfynd.xlsx
@@ -3239,7 +3239,7 @@
         <v>125830789</v>
       </c>
       <c r="B25" t="n">
-        <v>103770</v>
+        <v>103772</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>125830768</v>
       </c>
       <c r="B26" t="n">
-        <v>100521</v>
+        <v>100523</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         <v>125830803</v>
       </c>
       <c r="B27" t="n">
-        <v>101425</v>
+        <v>101427</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 57321-2024 artfynd.xlsx
+++ b/artfynd/A 57321-2024 artfynd.xlsx
@@ -3239,7 +3239,7 @@
         <v>125830789</v>
       </c>
       <c r="B25" t="n">
-        <v>103772</v>
+        <v>103774</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>125830768</v>
       </c>
       <c r="B26" t="n">
-        <v>100523</v>
+        <v>100525</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         <v>125830803</v>
       </c>
       <c r="B27" t="n">
-        <v>101427</v>
+        <v>101429</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 57321-2024 artfynd.xlsx
+++ b/artfynd/A 57321-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3239,7 +3239,7 @@
         <v>125830789</v>
       </c>
       <c r="B25" t="n">
-        <v>103774</v>
+        <v>103778</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>125830768</v>
       </c>
       <c r="B26" t="n">
-        <v>100525</v>
+        <v>100527</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         <v>125830803</v>
       </c>
       <c r="B27" t="n">
-        <v>101429</v>
+        <v>101431</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3555,6 +3555,444 @@
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>126301457</v>
+      </c>
+      <c r="B28" t="n">
+        <v>96471</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>2869</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Sphagnum wulfianum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Knapptjärn/Gölbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>534778</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6671654</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>126301498</v>
+      </c>
+      <c r="B29" t="n">
+        <v>100527</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Knapptjärn/Gölbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>534879</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6671662</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Inom kulturmijöhänsyn</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Lågörtbarrskog</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>126301477</v>
+      </c>
+      <c r="B30" t="n">
+        <v>98265</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Knapptjärn/Gölbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>534789</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6671626</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Avverkningsanmält</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>126301411</v>
+      </c>
+      <c r="B31" t="n">
+        <v>98265</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Knapptjärn/Gölbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>534748</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6671807</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 57321-2024 artfynd.xlsx
+++ b/artfynd/A 57321-2024 artfynd.xlsx
@@ -3239,7 +3239,7 @@
         <v>125830789</v>
       </c>
       <c r="B25" t="n">
-        <v>103778</v>
+        <v>103791</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>125830768</v>
       </c>
       <c r="B26" t="n">
-        <v>100527</v>
+        <v>100531</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         <v>125830803</v>
       </c>
       <c r="B27" t="n">
-        <v>101431</v>
+        <v>101435</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>126301457</v>
       </c>
       <c r="B28" t="n">
-        <v>96471</v>
+        <v>96475</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>126301498</v>
       </c>
       <c r="B29" t="n">
-        <v>100527</v>
+        <v>100531</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>126301477</v>
       </c>
       <c r="B30" t="n">
-        <v>98265</v>
+        <v>98269</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
         <v>126301411</v>
       </c>
       <c r="B31" t="n">
-        <v>98265</v>
+        <v>98269</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 57321-2024 artfynd.xlsx
+++ b/artfynd/A 57321-2024 artfynd.xlsx
@@ -3239,7 +3239,7 @@
         <v>125830789</v>
       </c>
       <c r="B25" t="n">
-        <v>103791</v>
+        <v>103794</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>125830768</v>
       </c>
       <c r="B26" t="n">
-        <v>100531</v>
+        <v>100534</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         <v>125830803</v>
       </c>
       <c r="B27" t="n">
-        <v>101435</v>
+        <v>101438</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>126301457</v>
       </c>
       <c r="B28" t="n">
-        <v>96475</v>
+        <v>96478</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>126301498</v>
       </c>
       <c r="B29" t="n">
-        <v>100531</v>
+        <v>100534</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>126301477</v>
       </c>
       <c r="B30" t="n">
-        <v>98269</v>
+        <v>98272</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
         <v>126301411</v>
       </c>
       <c r="B31" t="n">
-        <v>98269</v>
+        <v>98272</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 57321-2024 artfynd.xlsx
+++ b/artfynd/A 57321-2024 artfynd.xlsx
@@ -3239,7 +3239,7 @@
         <v>125830789</v>
       </c>
       <c r="B25" t="n">
-        <v>103794</v>
+        <v>103803</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>125830768</v>
       </c>
       <c r="B26" t="n">
-        <v>100534</v>
+        <v>100543</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         <v>125830803</v>
       </c>
       <c r="B27" t="n">
-        <v>101438</v>
+        <v>101447</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>126301457</v>
       </c>
       <c r="B28" t="n">
-        <v>96478</v>
+        <v>96487</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>126301498</v>
       </c>
       <c r="B29" t="n">
-        <v>100534</v>
+        <v>100543</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>126301477</v>
       </c>
       <c r="B30" t="n">
-        <v>98272</v>
+        <v>98281</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
         <v>126301411</v>
       </c>
       <c r="B31" t="n">
-        <v>98272</v>
+        <v>98281</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 57321-2024 artfynd.xlsx
+++ b/artfynd/A 57321-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AY34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3993,6 +3993,358 @@
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>127819880</v>
+      </c>
+      <c r="B32" t="n">
+        <v>92029</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Gölbäckens gammalskog, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>535002</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6671760</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Alec Bailey, Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>127820168</v>
+      </c>
+      <c r="B33" t="n">
+        <v>96702</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>53</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Gölbäckens gammalskog, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>535006</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6671736</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Alec Bailey, Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>127820111</v>
+      </c>
+      <c r="B34" t="n">
+        <v>92640</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>4368</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Dofttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Hydnellum suaveolens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Gölbäckens gammalskog, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>535006</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6671736</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Alec Bailey, Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 57321-2024 artfynd.xlsx
+++ b/artfynd/A 57321-2024 artfynd.xlsx
@@ -3998,7 +3998,7 @@
         <v>127819880</v>
       </c>
       <c r="B32" t="n">
-        <v>92029</v>
+        <v>92035</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         <v>127820168</v>
       </c>
       <c r="B33" t="n">
-        <v>96702</v>
+        <v>96708</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4241,7 +4241,7 @@
         <v>127820111</v>
       </c>
       <c r="B34" t="n">
-        <v>92640</v>
+        <v>92646</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Alec Bailey, Janolof Hermansson</t>
+          <t>Janolof Hermansson, Alec Bailey</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>

--- a/artfynd/A 57321-2024 artfynd.xlsx
+++ b/artfynd/A 57321-2024 artfynd.xlsx
@@ -3998,7 +3998,7 @@
         <v>127819880</v>
       </c>
       <c r="B32" t="n">
-        <v>92035</v>
+        <v>92038</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         <v>127820168</v>
       </c>
       <c r="B33" t="n">
-        <v>96708</v>
+        <v>96711</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4241,7 +4241,7 @@
         <v>127820111</v>
       </c>
       <c r="B34" t="n">
-        <v>92646</v>
+        <v>92649</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Alec Bailey</t>
+          <t>Alec Bailey, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>

--- a/artfynd/A 57321-2024 artfynd.xlsx
+++ b/artfynd/A 57321-2024 artfynd.xlsx
@@ -3998,7 +3998,7 @@
         <v>127819880</v>
       </c>
       <c r="B32" t="n">
-        <v>92038</v>
+        <v>92046</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         <v>127820168</v>
       </c>
       <c r="B33" t="n">
-        <v>96711</v>
+        <v>96719</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4241,7 +4241,7 @@
         <v>127820111</v>
       </c>
       <c r="B34" t="n">
-        <v>92649</v>
+        <v>92657</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 57321-2024 artfynd.xlsx
+++ b/artfynd/A 57321-2024 artfynd.xlsx
@@ -3998,7 +3998,7 @@
         <v>127819880</v>
       </c>
       <c r="B32" t="n">
-        <v>92046</v>
+        <v>92047</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         <v>127820168</v>
       </c>
       <c r="B33" t="n">
-        <v>96719</v>
+        <v>96720</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Alec Bailey, Janolof Hermansson</t>
+          <t>Janolof Hermansson, Alec Bailey</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4241,7 +4241,7 @@
         <v>127820111</v>
       </c>
       <c r="B34" t="n">
-        <v>92657</v>
+        <v>92658</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 57321-2024 artfynd.xlsx
+++ b/artfynd/A 57321-2024 artfynd.xlsx
@@ -4231,7 +4231,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Alec Bailey</t>
+          <t>Alec Bailey, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>

--- a/artfynd/A 57321-2024 artfynd.xlsx
+++ b/artfynd/A 57321-2024 artfynd.xlsx
@@ -3998,7 +3998,7 @@
         <v>127819880</v>
       </c>
       <c r="B32" t="n">
-        <v>92047</v>
+        <v>92048</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         <v>127820168</v>
       </c>
       <c r="B33" t="n">
-        <v>96720</v>
+        <v>96721</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4241,7 +4241,7 @@
         <v>127820111</v>
       </c>
       <c r="B34" t="n">
-        <v>92658</v>
+        <v>92659</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 57321-2024 artfynd.xlsx
+++ b/artfynd/A 57321-2024 artfynd.xlsx
@@ -3998,7 +3998,7 @@
         <v>127819880</v>
       </c>
       <c r="B32" t="n">
-        <v>92048</v>
+        <v>92049</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         <v>127820168</v>
       </c>
       <c r="B33" t="n">
-        <v>96721</v>
+        <v>96722</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4241,7 +4241,7 @@
         <v>127820111</v>
       </c>
       <c r="B34" t="n">
-        <v>92659</v>
+        <v>92660</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 57321-2024 artfynd.xlsx
+++ b/artfynd/A 57321-2024 artfynd.xlsx
@@ -3998,7 +3998,7 @@
         <v>127819880</v>
       </c>
       <c r="B32" t="n">
-        <v>92049</v>
+        <v>92057</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         <v>127820168</v>
       </c>
       <c r="B33" t="n">
-        <v>96722</v>
+        <v>96730</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4241,7 +4241,7 @@
         <v>127820111</v>
       </c>
       <c r="B34" t="n">
-        <v>92660</v>
+        <v>92668</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 57321-2024 artfynd.xlsx
+++ b/artfynd/A 57321-2024 artfynd.xlsx
@@ -3998,7 +3998,7 @@
         <v>127819880</v>
       </c>
       <c r="B32" t="n">
-        <v>92057</v>
+        <v>92149</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         <v>127820168</v>
       </c>
       <c r="B33" t="n">
-        <v>96730</v>
+        <v>96823</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4241,7 +4241,7 @@
         <v>127820111</v>
       </c>
       <c r="B34" t="n">
-        <v>92668</v>
+        <v>92760</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 57321-2024 artfynd.xlsx
+++ b/artfynd/A 57321-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AY35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4345,6 +4345,137 @@
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>129846284</v>
+      </c>
+      <c r="B35" t="n">
+        <v>92311</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Gölbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>534990</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6671767</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>kontinuitetsskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 57321-2024 artfynd.xlsx
+++ b/artfynd/A 57321-2024 artfynd.xlsx
@@ -4350,7 +4350,7 @@
         <v>129846284</v>
       </c>
       <c r="B35" t="n">
-        <v>92311</v>
+        <v>92315</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 57321-2024 artfynd.xlsx
+++ b/artfynd/A 57321-2024 artfynd.xlsx
@@ -4350,7 +4350,7 @@
         <v>129846284</v>
       </c>
       <c r="B35" t="n">
-        <v>92315</v>
+        <v>92317</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 57321-2024 artfynd.xlsx
+++ b/artfynd/A 57321-2024 artfynd.xlsx
@@ -4350,7 +4350,7 @@
         <v>129846284</v>
       </c>
       <c r="B35" t="n">
-        <v>92317</v>
+        <v>92320</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 57321-2024 artfynd.xlsx
+++ b/artfynd/A 57321-2024 artfynd.xlsx
@@ -4350,7 +4350,7 @@
         <v>129846284</v>
       </c>
       <c r="B35" t="n">
-        <v>92320</v>
+        <v>92323</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 57321-2024 artfynd.xlsx
+++ b/artfynd/A 57321-2024 artfynd.xlsx
@@ -4350,7 +4350,7 @@
         <v>129846284</v>
       </c>
       <c r="B35" t="n">
-        <v>92323</v>
+        <v>92324</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 57321-2024 artfynd.xlsx
+++ b/artfynd/A 57321-2024 artfynd.xlsx
@@ -4350,7 +4350,7 @@
         <v>129846284</v>
       </c>
       <c r="B35" t="n">
-        <v>92324</v>
+        <v>92341</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 57321-2024 artfynd.xlsx
+++ b/artfynd/A 57321-2024 artfynd.xlsx
@@ -4350,7 +4350,7 @@
         <v>129846284</v>
       </c>
       <c r="B35" t="n">
-        <v>92357</v>
+        <v>92359</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 57321-2024 artfynd.xlsx
+++ b/artfynd/A 57321-2024 artfynd.xlsx
@@ -4350,7 +4350,7 @@
         <v>129846284</v>
       </c>
       <c r="B35" t="n">
-        <v>92359</v>
+        <v>92446</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 57321-2024 artfynd.xlsx
+++ b/artfynd/A 57321-2024 artfynd.xlsx
@@ -4350,7 +4350,7 @@
         <v>129846284</v>
       </c>
       <c r="B35" t="n">
-        <v>92446</v>
+        <v>92359</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 57321-2024 artfynd.xlsx
+++ b/artfynd/A 57321-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AY58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>76137224</v>
+        <v>102228077</v>
       </c>
       <c r="B2" t="n">
-        <v>85234</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,44 +686,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>454</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rovspindling</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius napus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Fr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lönnsvadberget, Söderbärke, Dlr</t>
+          <t>Gölbäcken - Knapptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>534994.928557282</v>
+        <v>534956</v>
       </c>
       <c r="R2" t="n">
-        <v>6671741.02408978</v>
+        <v>6671789</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,27 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2008-09-01</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2008-09-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Medexkurenter var även Sören Gutén och Magnus Gustafsson</t>
+          <t>2022-07-11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,80 +764,86 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Lågörtbarrskog</t>
+          <t>Blåbärsbarrskog</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Rikmarkspåverkan</t>
+          <t>naturskog, nyckelbiotop</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>gammal granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Janols</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Janols, Janolof Hermansson, Uno Skog</t>
+          <t>Janolof Hermansson, Stig-Åke Svenson, Åke Persson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118074415</v>
+        <v>121853328</v>
       </c>
       <c r="B3" t="n">
-        <v>100107</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Knapptjärn, Dlr</t>
+          <t>Gölbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>534955</v>
+        <v>534995</v>
       </c>
       <c r="R3" t="n">
-        <v>6671722</v>
+        <v>6671743</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,12 +867,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Gysinge Skog naturvärdesbedömning.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,76 +886,76 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>gammal barrblandskog med tjock mossmatta</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>tallåga över bäck</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Stig-Åke Svenson</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Stig-Åke Svenson, Åke Persson</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119057996</v>
+        <v>121853353</v>
       </c>
       <c r="B4" t="n">
-        <v>100150</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gölbäcken - Kapptjärn, Dlr</t>
+          <t>Gölbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>534905</v>
+        <v>535035</v>
       </c>
       <c r="R4" t="n">
-        <v>6671685</v>
+        <v>6671840</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -991,12 +979,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Gysinge Skog naturvärdesbedömning.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,74 +998,73 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>äldre granskog med tjock mossmatta</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Nadja Hermansson Kovler</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119294603</v>
+        <v>121853354</v>
       </c>
       <c r="B5" t="n">
-        <v>103418</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222412</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fräkenkärret, Fräkenkärret, Dlr</t>
+          <t>Gölbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>534885</v>
+        <v>534971</v>
       </c>
       <c r="R5" t="n">
-        <v>6671725</v>
+        <v>6671775</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1099,12 +1091,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Gysinge Skog naturvärdesbedömning.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,69 +1112,78 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>gammal blåbärsgranskog vid bäck</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>granlåga över bäck</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Stig-Åke Svenson</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119294689</v>
+        <v>127819509</v>
       </c>
       <c r="B6" t="n">
-        <v>100171</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Fräkenkärret, Fräkenkärret, Dlr</t>
+          <t>Gölbäckens gammalskog, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>534895</v>
+        <v>535022</v>
       </c>
       <c r="R6" t="n">
-        <v>6671684</v>
+        <v>6671849</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1201,12 +1207,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,33 +1221,49 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Stig-Åke Svenson</t>
+          <t>Alec Bailey, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119294187</v>
+        <v>127820168</v>
       </c>
       <c r="B7" t="n">
-        <v>91842</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1249,37 +1271,41 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>788</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fräkenkärret, Fräkenkärret, Dlr</t>
+          <t>Gölbäckens gammalskog, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>534878</v>
+        <v>535006</v>
       </c>
       <c r="R7" t="n">
-        <v>6671746</v>
+        <v>6671736</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1303,12 +1329,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,71 +1343,94 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Stig-Åke Svenson</t>
+          <t>Alec Bailey, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119295534</v>
+        <v>76137224</v>
       </c>
       <c r="B8" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87300</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>454</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rovspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cortinarius napus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fräkenkärret, Fräkenkärret, Dlr</t>
+          <t>Lönnsvadberget, Söderbärke, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>534987</v>
+        <v>534995</v>
       </c>
       <c r="R8" t="n">
-        <v>6671767</v>
+        <v>6671741</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1405,12 +1454,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2008-09-01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2008-09-01</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Medexkurenter var även Sören Gutén och Magnus Gustafsson</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,33 +1473,39 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Lågörtbarrskog</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Rikmarkspåverkan</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Anders Janols</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Stig-Åke Svenson</t>
+          <t>Anders Janols, Janolof Hermansson, Uno Skog</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119295583</v>
+        <v>119294187</v>
       </c>
       <c r="B9" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93199</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1453,21 +1513,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>788</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1477,10 +1537,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>534962</v>
+        <v>534878</v>
       </c>
       <c r="R9" t="n">
-        <v>6671760</v>
+        <v>6671746</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1539,53 +1599,58 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119294755</v>
+        <v>67601773</v>
       </c>
       <c r="B10" t="n">
-        <v>91494</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92147</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4769</v>
+        <v>1101</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Peck) Jülich</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fräkenkärret, Fräkenkärret, Dlr</t>
+          <t>Gölbäcken, O om Knapptjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>534906</v>
+        <v>534899</v>
       </c>
       <c r="R10" t="n">
-        <v>6671703</v>
+        <v>6671788</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1609,12 +1674,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2017-09-17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2017-09-17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1623,71 +1688,95 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>mossig barrskog med gamla tallar</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>på rotben # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Stig-Åke Svenson</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119295577</v>
+        <v>109971242</v>
       </c>
       <c r="B11" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fräkenkärret, Fräkenkärret, Dlr</t>
+          <t>Gölbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>534982</v>
+        <v>534809</v>
       </c>
       <c r="R11" t="n">
-        <v>6671760</v>
+        <v>6671806</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1711,12 +1800,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2023-06-10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2023-06-10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1725,68 +1814,79 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Lågörtbarrskog</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>naturskog</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Stig-Åke Svenson</t>
+          <t>Janolof Hermansson, Bengt Lundborg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119889427</v>
+        <v>121853326</v>
       </c>
       <c r="B12" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gölbäcken, Gölbäcken, Dlr</t>
+          <t>Gölbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>534759</v>
+        <v>534960</v>
       </c>
       <c r="R12" t="n">
-        <v>6671790</v>
+        <v>6671792</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1813,22 +1913,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>13:49</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>13:49</t>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Gysinge Skog naturvärdesbedömning.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1839,69 +1934,72 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>gammal barrblandskog med tjock mossmatta</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119889464</v>
+        <v>75213796</v>
       </c>
       <c r="B13" t="n">
-        <v>97847</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219790</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gölbäcken, Gölbäcken, Dlr</t>
+          <t>Gölbäcken, O om Knapptjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>534747</v>
+        <v>535024</v>
       </c>
       <c r="R13" t="n">
         <v>6671800</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1925,22 +2023,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>13:51</t>
+          <t>2018-12-08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>13:51</t>
+          <t>2018-12-08</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1949,80 +2037,95 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>naturskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>granlåga # Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119889108</v>
+        <v>119983043</v>
       </c>
       <c r="B14" t="n">
-        <v>91512</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4769</v>
+        <v>1209</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gölbäcken, Gölbäcken, Dlr</t>
+          <t>Knapptjärn/Gölbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>534842</v>
+        <v>535007</v>
       </c>
       <c r="R14" t="n">
-        <v>6671768</v>
+        <v>6671754</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2049,92 +2152,111 @@
           <t>2024-09-21</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>13:43</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-21</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>13:43</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>naturskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Janolof Hermansson, Stig-Åke Svenson, Cecilia Rastad, Åke Persson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119888431</v>
+        <v>119984203</v>
       </c>
       <c r="B15" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gölbäcken, Gölbäcken, Dlr</t>
+          <t>Knapptjärn/Gölbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>534953</v>
+        <v>534913</v>
       </c>
       <c r="R15" t="n">
-        <v>6671754</v>
+        <v>6671750</v>
       </c>
       <c r="S15" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2161,81 +2283,72 @@
           <t>2024-09-21</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-21</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Knärot precis invid markeringen för avverkning vägen genom nyckelbiotopen.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>naturskog</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Janolof Hermansson, Stig-Åke Svenson, Cecilia Rastad, Åke Persson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119888281</v>
+        <v>121853325</v>
       </c>
       <c r="B16" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2245,10 +2358,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>534939</v>
+        <v>534960</v>
       </c>
       <c r="R16" t="n">
-        <v>6671725</v>
+        <v>6671792</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2275,22 +2388,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>13:26</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>13:26</t>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Gysinge Skog naturvärdesbedömning.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2301,69 +2409,81 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>gammal barrblandskog med tjock mossmatta</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119889540</v>
+        <v>129846293</v>
       </c>
       <c r="B17" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Fräkenkärret, Dlr</t>
+          <t>Gölbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>534957</v>
+        <v>535006</v>
       </c>
       <c r="R17" t="n">
-        <v>6671726</v>
+        <v>6671790</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2387,22 +2507,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>13:56</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>13:56</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2411,76 +2521,94 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>kontinuitetsskog</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>marken</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Staffan Jansson</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Staffan Jansson</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119889221</v>
+        <v>126301457</v>
       </c>
       <c r="B18" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Gölbäcken, Gölbäcken, Dlr</t>
+          <t>Knapptjärn/Gölbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>534821</v>
+        <v>534778</v>
       </c>
       <c r="R18" t="n">
-        <v>6671773</v>
+        <v>6671654</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2504,22 +2632,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>13:45</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>13:45</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2528,75 +2646,75 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119927799</v>
+        <v>127819880</v>
       </c>
       <c r="B19" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Gölbäcken, Dlr</t>
+          <t>Gölbäckens gammalskog, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>534969</v>
+        <v>535002</v>
       </c>
       <c r="R19" t="n">
-        <v>6671737</v>
+        <v>6671760</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2620,12 +2738,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2638,58 +2756,72 @@
       <c r="AG19" t="b">
         <v>0</v>
       </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Stig-Åke Svenson</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Stig-Åke Svenson</t>
+          <t>Alec Bailey, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119927817</v>
+        <v>129846284</v>
       </c>
       <c r="B20" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2697,10 +2829,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>534963</v>
+        <v>534990</v>
       </c>
       <c r="R20" t="n">
-        <v>6671740</v>
+        <v>6671767</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2727,12 +2859,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2745,72 +2877,104 @@
       <c r="AG20" t="b">
         <v>0</v>
       </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>kontinuitetsskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Stig-Åke Svenson</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Stig-Åke Svenson</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119927788</v>
+        <v>127820111</v>
       </c>
       <c r="B21" t="n">
-        <v>100194</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93215</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>4368</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Gölbäcken, Dlr</t>
+          <t>Gölbäckens gammalskog, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>534956</v>
+        <v>535006</v>
       </c>
       <c r="R21" t="n">
-        <v>6671735</v>
+        <v>6671736</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2834,12 +2998,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2855,68 +3019,60 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Stig-Åke Svenson</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Stig-Åke Svenson</t>
+          <t>Alec Bailey, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119984203</v>
+        <v>119294755</v>
       </c>
       <c r="B22" t="n">
-        <v>91023</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1209</v>
+        <v>4769</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Knapptjärn/Gölbäcken, Dlr</t>
+          <t>Fräkenkärret, Fräkenkärret, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>534913</v>
+        <v>534906</v>
       </c>
       <c r="R22" t="n">
-        <v>6671750</v>
+        <v>6671703</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2940,12 +3096,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2954,85 +3110,75 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>naturskog</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Stig-Åke Svenson, Cecilia Rastad, Åke Persson</t>
+          <t>Patric Engfeldt, Stig-Åke Svenson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119983043</v>
+        <v>119889108</v>
       </c>
       <c r="B23" t="n">
-        <v>91023</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1209</v>
+        <v>4769</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Knapptjärn/Gölbäcken, Dlr</t>
+          <t>Gölbäcken, Gölbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>535007</v>
+        <v>534842</v>
       </c>
       <c r="R23" t="n">
-        <v>6671754</v>
+        <v>6671768</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3059,97 +3205,71 @@
           <t>2024-09-21</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-09-21</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>naturskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Stig-Åke Svenson, Cecilia Rastad, Åke Persson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121853328</v>
+        <v>121853351</v>
       </c>
       <c r="B24" t="n">
-        <v>95722</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3159,10 +3279,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>534995</v>
+        <v>535076</v>
       </c>
       <c r="R24" t="n">
-        <v>6671743</v>
+        <v>6671855</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3189,12 +3309,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3213,12 +3333,12 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>gammal barrblandskog med tjock mossmatta</t>
+          <t>äldre granskog med tjock mossmatta</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>tallåga över bäck</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3236,49 +3356,53 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125830789</v>
+        <v>109971233</v>
       </c>
       <c r="B25" t="n">
-        <v>103803</v>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222412</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Gölbäcken - Knapptjärn, Dlr</t>
+          <t>Gölbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>534901</v>
+        <v>534809</v>
       </c>
       <c r="R25" t="n">
-        <v>6671688</v>
+        <v>6671806</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3305,12 +3429,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2023-06-10</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2023-06-10</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>hackspår i gammal gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3319,14 +3448,8 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3336,59 +3459,60 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Åke Persson</t>
+          <t>Janolof Hermansson, Bengt Lundborg</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125830768</v>
+        <v>121853330</v>
       </c>
       <c r="B26" t="n">
-        <v>100543</v>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Gölbäcken - Knapptjärn, Dlr</t>
+          <t>Gölbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>534901</v>
+        <v>534807</v>
       </c>
       <c r="R26" t="n">
-        <v>6671688</v>
+        <v>6671801</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3412,12 +3536,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Gysinge Skog naturvärdesbedömning.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3426,34 +3555,38 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>gammal barrblandskog med tjock mossmatta</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Åke Persson</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125830803</v>
+        <v>119889464</v>
       </c>
       <c r="B27" t="n">
-        <v>101447</v>
+        <v>99035</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3461,41 +3594,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221235</v>
+        <v>219790</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Gölbäcken - Knapptjärn, Dlr</t>
+          <t>Gölbäcken, Gölbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>534901</v>
+        <v>534747</v>
       </c>
       <c r="R27" t="n">
-        <v>6671688</v>
+        <v>6671800</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3519,12 +3648,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3533,81 +3672,71 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Åke Persson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126301457</v>
+        <v>88075747</v>
       </c>
       <c r="B28" t="n">
-        <v>96487</v>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Knapptjärn/Gölbäcken, Dlr</t>
+          <t>Gölbäcken Smedjebacken, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>534778</v>
+        <v>534996</v>
       </c>
       <c r="R28" t="n">
-        <v>6671654</v>
+        <v>6671715</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3634,12 +3763,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2020-09-19</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2020-09-19</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3652,69 +3791,72 @@
       <c r="AG28" t="b">
         <v>0</v>
       </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
-        </is>
-      </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Lena Stigsdotter</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Lena Stigsdotter</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126301498</v>
+        <v>109971207</v>
       </c>
       <c r="B29" t="n">
-        <v>100543</v>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Knapptjärn/Gölbäcken, Dlr</t>
+          <t>Gölbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>534879</v>
+        <v>534791</v>
       </c>
       <c r="R29" t="n">
-        <v>6671662</v>
+        <v>6671816</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3741,17 +3883,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2023-06-10</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Inom kulturmijöhänsyn</t>
+          <t>2023-06-10</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3769,6 +3906,11 @@
           <t>Lågörtbarrskog</t>
         </is>
       </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>naturskog</t>
+        </is>
+      </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
@@ -3777,55 +3919,55 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Janolof Hermansson, Bengt Lundborg</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126301477</v>
+        <v>119294425</v>
       </c>
       <c r="B30" t="n">
-        <v>98281</v>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>223597</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Knapptjärn/Gölbäcken, Dlr</t>
+          <t>Fräkenkärret, Fräkenkärret, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>534789</v>
+        <v>534910</v>
       </c>
       <c r="R30" t="n">
-        <v>6671626</v>
+        <v>6671796</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3849,17 +3991,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Avverkningsanmält</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3868,72 +4005,66 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Patric Engfeldt, Stig-Åke Svenson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126301411</v>
+        <v>119295534</v>
       </c>
       <c r="B31" t="n">
-        <v>98281</v>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>223597</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Knapptjärn/Gölbäcken, Dlr</t>
+          <t>Fräkenkärret, Fräkenkärret, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>534748</v>
+        <v>534987</v>
       </c>
       <c r="R31" t="n">
-        <v>6671807</v>
+        <v>6671767</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3957,12 +4088,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3971,75 +4102,66 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Patric Engfeldt, Stig-Åke Svenson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127819880</v>
+        <v>119295577</v>
       </c>
       <c r="B32" t="n">
-        <v>92149</v>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Gölbäckens gammalskog, Dlr</t>
+          <t>Fräkenkärret, Fräkenkärret, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>535002</v>
+        <v>534982</v>
       </c>
       <c r="R32" t="n">
         <v>6671760</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4063,12 +4185,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4077,91 +4199,66 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Alec Bailey, Janolof Hermansson</t>
+          <t>Patric Engfeldt, Stig-Åke Svenson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127820168</v>
+        <v>119295583</v>
       </c>
       <c r="B33" t="n">
-        <v>96823</v>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Gölbäckens gammalskog, Dlr</t>
+          <t>Fräkenkärret, Fräkenkärret, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>535006</v>
+        <v>534962</v>
       </c>
       <c r="R33" t="n">
-        <v>6671736</v>
+        <v>6671760</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4185,12 +4282,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4199,98 +4296,66 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Alec Bailey, Janolof Hermansson</t>
+          <t>Patric Engfeldt, Stig-Åke Svenson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127820111</v>
+        <v>119888281</v>
       </c>
       <c r="B34" t="n">
-        <v>92760</v>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4368</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Gölbäckens gammalskog, Dlr</t>
+          <t>Gölbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>535006</v>
+        <v>534939</v>
       </c>
       <c r="R34" t="n">
-        <v>6671736</v>
+        <v>6671725</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4314,12 +4379,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4328,70 +4403,66 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Alec Bailey, Janolof Hermansson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129846284</v>
+        <v>119888431</v>
       </c>
       <c r="B35" t="n">
-        <v>92359</v>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Gölbäcken, Dlr</t>
+          <t>Gölbäcken, Gölbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>534990</v>
+        <v>534953</v>
       </c>
       <c r="R35" t="n">
-        <v>6671767</v>
+        <v>6671754</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4415,12 +4486,27 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Knärot precis invid markeringen för avverkning vägen genom nyckelbiotopen.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4429,52 +4515,2468 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>kontinuitetsskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>119889221</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Gölbäcken, Gölbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>534821</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6671773</v>
+      </c>
+      <c r="S36" t="n">
+        <v>25</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>119889427</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Gölbäcken, Gölbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>534759</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6671790</v>
+      </c>
+      <c r="S37" t="n">
+        <v>25</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>119889540</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Fräkenkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>534957</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6671726</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Staffan Jansson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Staffan Jansson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>119889607</v>
+      </c>
+      <c r="B39" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Fräkenkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>534983</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6671688</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Staffan Jansson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Staffan Jansson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>119927799</v>
+      </c>
+      <c r="B40" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Gölbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>534969</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6671737</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Stig-Åke Svenson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Stig-Åke Svenson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>119927817</v>
+      </c>
+      <c r="B41" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Gölbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>534963</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6671740</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Stig-Åke Svenson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Stig-Åke Svenson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>121853329</v>
+      </c>
+      <c r="B42" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Gölbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>534801</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6671794</v>
+      </c>
+      <c r="S42" t="n">
+        <v>25</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Gysinge Skog naturvärdesbedömning.</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>gammal barrblandskog med tjock mossmatta</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>125831076</v>
+      </c>
+      <c r="B43" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Gölbäcken - Knapptjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>534962</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6671779</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>grov mossig granlåga</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
           <t>Janolof Hermansson</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson, Åke Persson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>127819624</v>
+      </c>
+      <c r="B44" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Gölbäckens gammalskog, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>535048</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6671847</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson, Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>127819733</v>
+      </c>
+      <c r="B45" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Gölbäckens gammalskog, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>535016</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6671800</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Alec Bailey, Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>125830803</v>
+      </c>
+      <c r="B46" t="n">
+        <v>102241</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Gölbäcken - Knapptjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>534901</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6671688</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
         <is>
           <t>Janolof Hermansson</t>
         </is>
       </c>
-      <c r="AY35" t="inlineStr"/>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson, Åke Persson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>67601802</v>
+      </c>
+      <c r="B47" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Gölbäcken, O om Knapptjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>534847</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6671789</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2017-09-17</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2017-09-17</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Alsumpskog</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>litet klibbalkärr</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>119294603</v>
+      </c>
+      <c r="B48" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Fräkenkärret, Fräkenkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>534885</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6671725</v>
+      </c>
+      <c r="S48" t="n">
+        <v>25</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt, Stig-Åke Svenson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>125830603</v>
+      </c>
+      <c r="B49" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Gölbäcken - Knapptjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>535006</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6671720</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>nära bäcken</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson, Åke Persson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>125830789</v>
+      </c>
+      <c r="B50" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Gölbäcken - Knapptjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>534901</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6671688</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson, Åke Persson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>118074415</v>
+      </c>
+      <c r="B51" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Knapptjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>534955</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6671722</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2024-06-18</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2024-06-18</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Stig-Åke Svenson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Stig-Åke Svenson, Åke Persson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>119057996</v>
+      </c>
+      <c r="B52" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Gölbäcken - Kapptjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>534905</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6671685</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2024-08-11</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2024-08-11</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson, Nadja Hermansson Kovler</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>119294689</v>
+      </c>
+      <c r="B53" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Fräkenkärret, Fräkenkärret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>534895</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6671684</v>
+      </c>
+      <c r="S53" t="n">
+        <v>25</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt, Stig-Åke Svenson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>119927788</v>
+      </c>
+      <c r="B54" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Gölbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>534956</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6671735</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Stig-Åke Svenson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Stig-Åke Svenson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>125830768</v>
+      </c>
+      <c r="B55" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Gölbäcken - Knapptjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>534901</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6671688</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson, Åke Persson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>126301498</v>
+      </c>
+      <c r="B56" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Knapptjärn/Gölbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>534879</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6671662</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Inom kulturmijöhänsyn</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>Lågörtbarrskog</t>
+        </is>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>126301411</v>
+      </c>
+      <c r="B57" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Knapptjärn/Gölbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>534748</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6671807</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>126301477</v>
+      </c>
+      <c r="B58" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Knapptjärn/Gölbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>534789</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6671626</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Avverkningsanmält</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 57321-2024 artfynd.xlsx
+++ b/artfynd/A 57321-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY58"/>
+  <dimension ref="A1:AZ58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -799,6 +804,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102228077</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -911,6 +921,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121853328</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1023,6 +1038,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121853353</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1135,6 +1155,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121853354</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1257,6 +1282,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127819509</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1379,6 +1409,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127820168</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1499,6 +1534,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76137224</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1596,6 +1636,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119294187</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1729,6 +1774,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67601773</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1845,6 +1895,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109971242</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1952,6 +2007,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121853326</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2078,6 +2138,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75213796</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2209,6 +2274,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119983043</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2320,6 +2390,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119984203</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2427,6 +2502,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121853325</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2552,6 +2632,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129846293</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2667,6 +2752,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126301457</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2788,6 +2878,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127819880</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2919,6 +3014,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129846284</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3028,6 +3128,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127820111</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3125,6 +3230,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119294755</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3241,6 +3351,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119889108</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3353,6 +3468,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121853351</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3463,6 +3583,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109971233</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3580,6 +3705,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121853330</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3687,6 +3817,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119889464</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3803,6 +3938,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88075747</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3923,6 +4063,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109971207</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4020,6 +4165,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119294425</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4117,6 +4267,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119295534</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4214,6 +4369,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119295577</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4311,6 +4471,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119295583</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4418,6 +4583,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119888281</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4530,6 +4700,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119888431</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4642,6 +4817,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119889221</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4749,6 +4929,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119889427</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4856,6 +5041,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119889540</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4963,6 +5153,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119889607</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5065,6 +5260,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119927799</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5167,6 +5367,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119927817</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5274,6 +5479,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121853329</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5386,6 +5596,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125831076</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5496,6 +5711,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127819624</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5606,6 +5826,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127819733</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5713,6 +5938,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125830803</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5823,6 +6053,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67601802</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5920,6 +6155,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119294603</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6032,6 +6272,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125830603</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6139,6 +6384,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125830789</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6241,6 +6491,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118074415</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6348,6 +6603,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119057996</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6445,6 +6705,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119294689</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6547,6 +6812,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119927788</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6654,6 +6924,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125830768</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6766,6 +7041,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126301498</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6869,6 +7149,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126301411</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6977,8 +7262,72 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126301477</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 57321-2024 artfynd.xlsx
+++ b/artfynd/A 57321-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ58"/>
+  <dimension ref="A1:AZ62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5834,32 +5834,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125830803</v>
+        <v>136091903</v>
       </c>
       <c r="B46" t="n">
-        <v>102241</v>
+        <v>99293</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221235</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5869,14 +5869,14 @@
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Gölbäcken - Knapptjärn, Dlr</t>
+          <t>Gölbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>534901</v>
+        <v>534757</v>
       </c>
       <c r="R46" t="n">
-        <v>6671688</v>
+        <v>6671803</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5903,12 +5903,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5923,7 +5923,7 @@
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>Lågörtgranskog</t>
+          <t>Lågörtbarrskog</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5934,60 +5934,69 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Åke Persson</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125830803</t>
+          <t>https://artportalen.se/Sighting/136091903</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>67601802</v>
+        <v>136092022</v>
       </c>
       <c r="B47" t="n">
-        <v>97983</v>
+        <v>99293</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Gölbäcken, O om Knapptjärnsberget, Dlr</t>
+          <t>Gölbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>534847</v>
+        <v>534973</v>
       </c>
       <c r="R47" t="n">
-        <v>6671789</v>
+        <v>6671751</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -6014,12 +6023,17 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2017-09-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2017-09-17</t>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>tre ynkliga plantor. Verkar vara hämmade av torkan. Platsen snitslad som hänsynsyta på radie av 8 meter.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6028,17 +6042,13 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>Alsumpskog</t>
-        </is>
-      </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>litet klibbalkärr</t>
+          <t>Lågörtbarrskog</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6055,54 +6065,58 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67601802</t>
+          <t>https://artportalen.se/Sighting/136092022</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119294603</v>
+        <v>125830803</v>
       </c>
       <c r="B48" t="n">
-        <v>104628</v>
+        <v>102241</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>222412</v>
+        <v>221235</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Fräkenkärret, Fräkenkärret, Dlr</t>
+          <t>Gölbäcken - Knapptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>534885</v>
+        <v>534901</v>
       </c>
       <c r="R48" t="n">
-        <v>6671725</v>
+        <v>6671688</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6126,12 +6140,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6140,33 +6154,39 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Stig-Åke Svenson</t>
+          <t>Janolof Hermansson, Åke Persson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119294603</t>
+          <t>https://artportalen.se/Sighting/125830803</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125830603</v>
+        <v>67601802</v>
       </c>
       <c r="B49" t="n">
-        <v>104628</v>
+        <v>97983</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6174,16 +6194,16 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>222412</v>
+        <v>221945</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -6195,17 +6215,16 @@
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Gölbäcken - Knapptjärn, Dlr</t>
+          <t>Gölbäcken, O om Knapptjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>535006</v>
+        <v>534847</v>
       </c>
       <c r="R49" t="n">
-        <v>6671720</v>
+        <v>6671789</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6232,12 +6251,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2017-09-17</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2017-09-17</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6246,18 +6265,17 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>Lågörtgranskog</t>
+          <t>Alsumpskog</t>
         </is>
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>nära bäcken</t>
+          <t>litet klibbalkärr</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6268,19 +6286,19 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Åke Persson</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125830603</t>
+          <t>https://artportalen.se/Sighting/67601802</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125830789</v>
+        <v>119294603</v>
       </c>
       <c r="B50" t="n">
         <v>104628</v>
@@ -6309,23 +6327,19 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Gölbäcken - Knapptjärn, Dlr</t>
+          <t>Fräkenkärret, Fräkenkärret, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>534901</v>
+        <v>534885</v>
       </c>
       <c r="R50" t="n">
-        <v>6671688</v>
+        <v>6671725</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6349,12 +6363,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6363,39 +6377,33 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Åke Persson</t>
+          <t>Patric Engfeldt, Stig-Åke Svenson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125830789</t>
+          <t>https://artportalen.se/Sighting/119294603</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118074415</v>
+        <v>125830603</v>
       </c>
       <c r="B51" t="n">
-        <v>101326</v>
+        <v>104628</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6403,21 +6411,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6427,14 +6435,14 @@
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Knapptjärn, Dlr</t>
+          <t>Gölbäcken - Knapptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>534955</v>
+        <v>535006</v>
       </c>
       <c r="R51" t="n">
-        <v>6671722</v>
+        <v>6671720</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6461,12 +6469,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6479,30 +6487,40 @@
       <c r="AG51" t="b">
         <v>0</v>
       </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>nära bäcken</t>
+        </is>
+      </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Stig-Åke Svenson</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Stig-Åke Svenson, Åke Persson</t>
+          <t>Janolof Hermansson, Åke Persson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118074415</t>
+          <t>https://artportalen.se/Sighting/125830603</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119057996</v>
+        <v>125830789</v>
       </c>
       <c r="B52" t="n">
-        <v>101326</v>
+        <v>104628</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6510,21 +6528,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6534,14 +6552,14 @@
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Gölbäcken - Kapptjärn, Dlr</t>
+          <t>Gölbäcken - Knapptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>534905</v>
+        <v>534901</v>
       </c>
       <c r="R52" t="n">
-        <v>6671685</v>
+        <v>6671688</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6568,12 +6586,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6599,19 +6617,19 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Nadja Hermansson Kovler</t>
+          <t>Janolof Hermansson, Åke Persson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119057996</t>
+          <t>https://artportalen.se/Sighting/125830789</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119294689</v>
+        <v>118074415</v>
       </c>
       <c r="B53" t="n">
         <v>101326</v>
@@ -6640,19 +6658,23 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Fräkenkärret, Fräkenkärret, Dlr</t>
+          <t>Knapptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>534895</v>
+        <v>534955</v>
       </c>
       <c r="R53" t="n">
-        <v>6671684</v>
+        <v>6671722</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6676,12 +6698,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6690,30 +6712,31 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Stig-Åke Svenson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Stig-Åke Svenson</t>
+          <t>Stig-Åke Svenson, Åke Persson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119294689</t>
+          <t>https://artportalen.se/Sighting/118074415</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119927788</v>
+        <v>119057996</v>
       </c>
       <c r="B54" t="n">
         <v>101326</v>
@@ -6748,14 +6771,14 @@
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Gölbäcken, Dlr</t>
+          <t>Gölbäcken - Kapptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>534956</v>
+        <v>534905</v>
       </c>
       <c r="R54" t="n">
-        <v>6671735</v>
+        <v>6671685</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6782,12 +6805,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-08-11</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-08-11</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6800,27 +6823,32 @@
       <c r="AG54" t="b">
         <v>0</v>
       </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Stig-Åke Svenson</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Stig-Åke Svenson</t>
+          <t>Janolof Hermansson, Nadja Hermansson Kovler</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119927788</t>
+          <t>https://artportalen.se/Sighting/119057996</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125830768</v>
+        <v>119294689</v>
       </c>
       <c r="B55" t="n">
         <v>101326</v>
@@ -6849,23 +6877,19 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Gölbäcken - Knapptjärn, Dlr</t>
+          <t>Fräkenkärret, Fräkenkärret, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>534901</v>
+        <v>534895</v>
       </c>
       <c r="R55" t="n">
-        <v>6671688</v>
+        <v>6671684</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6889,12 +6913,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6903,36 +6927,30 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Åke Persson</t>
+          <t>Patric Engfeldt, Stig-Åke Svenson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125830768</t>
+          <t>https://artportalen.se/Sighting/119294689</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126301498</v>
+        <v>119927788</v>
       </c>
       <c r="B56" t="n">
         <v>101326</v>
@@ -6967,14 +6985,14 @@
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Knapptjärn/Gölbäcken, Dlr</t>
+          <t>Gölbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>534879</v>
+        <v>534956</v>
       </c>
       <c r="R56" t="n">
-        <v>6671662</v>
+        <v>6671735</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7001,17 +7019,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Inom kulturmijöhänsyn</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7024,35 +7037,30 @@
       <c r="AG56" t="b">
         <v>0</v>
       </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>Lågörtbarrskog</t>
-        </is>
-      </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Stig-Åke Svenson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Stig-Åke Svenson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126301498</t>
+          <t>https://artportalen.se/Sighting/119927788</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126301411</v>
+        <v>125830768</v>
       </c>
       <c r="B57" t="n">
-        <v>99038</v>
+        <v>101326</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7060,19 +7068,23 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>223597</v>
+        <v>222498</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
@@ -7080,14 +7092,14 @@
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Knapptjärn/Gölbäcken, Dlr</t>
+          <t>Gölbäcken - Knapptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>534748</v>
+        <v>534901</v>
       </c>
       <c r="R57" t="n">
-        <v>6671807</v>
+        <v>6671688</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7114,12 +7126,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7134,7 +7146,7 @@
       </c>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Lågörtgranskog</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7145,22 +7157,22 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Janolof Hermansson, Åke Persson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126301411</t>
+          <t>https://artportalen.se/Sighting/125830768</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126301477</v>
+        <v>126301498</v>
       </c>
       <c r="B58" t="n">
-        <v>99038</v>
+        <v>101326</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7168,19 +7180,23 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>223597</v>
+        <v>222498</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
@@ -7192,10 +7208,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>534789</v>
+        <v>534879</v>
       </c>
       <c r="R58" t="n">
-        <v>6671626</v>
+        <v>6671662</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7232,7 +7248,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Avverkningsanmält</t>
+          <t>Inom kulturmijöhänsyn</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7247,7 +7263,7 @@
       </c>
       <c r="AH58" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Lågörtbarrskog</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7263,6 +7279,451 @@
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126301498</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>136091964</v>
+      </c>
+      <c r="B59" t="n">
+        <v>101502</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Gölbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>534902</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6671682</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>Lågörtbarrskog</t>
+        </is>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136091964</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>136091947</v>
+      </c>
+      <c r="B60" t="n">
+        <v>99570</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Gölbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>534900</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6671688</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>Lågörtbarrskog</t>
+        </is>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136091947</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>126301411</v>
+      </c>
+      <c r="B61" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Knapptjärn/Gölbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>534748</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6671807</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126301411</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>126301477</v>
+      </c>
+      <c r="B62" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Knapptjärn/Gölbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>534789</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6671626</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Avverkningsanmält</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/126301477</t>
         </is>
@@ -7327,6 +7788,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 57321-2024 artfynd.xlsx
+++ b/artfynd/A 57321-2024 artfynd.xlsx
@@ -5837,7 +5837,7 @@
         <v>136091903</v>
       </c>
       <c r="B46" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         <v>136092022</v>
       </c>
       <c r="B47" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -7289,7 +7289,7 @@
         <v>136091964</v>
       </c>
       <c r="B59" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7401,7 +7401,7 @@
         <v>136091947</v>
       </c>
       <c r="B60" t="n">
-        <v>99570</v>
+        <v>99571</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 57321-2024 artfynd.xlsx
+++ b/artfynd/A 57321-2024 artfynd.xlsx
@@ -5837,7 +5837,7 @@
         <v>136091903</v>
       </c>
       <c r="B46" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         <v>136092022</v>
       </c>
       <c r="B47" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -7289,7 +7289,7 @@
         <v>136091964</v>
       </c>
       <c r="B59" t="n">
-        <v>101504</v>
+        <v>101505</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7401,7 +7401,7 @@
         <v>136091947</v>
       </c>
       <c r="B60" t="n">
-        <v>99571</v>
+        <v>99572</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 57321-2024 artfynd.xlsx
+++ b/artfynd/A 57321-2024 artfynd.xlsx
@@ -5837,7 +5837,7 @@
         <v>136091903</v>
       </c>
       <c r="B46" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         <v>136092022</v>
       </c>
       <c r="B47" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -7289,7 +7289,7 @@
         <v>136091964</v>
       </c>
       <c r="B59" t="n">
-        <v>101505</v>
+        <v>101506</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7401,7 +7401,7 @@
         <v>136091947</v>
       </c>
       <c r="B60" t="n">
-        <v>99572</v>
+        <v>99573</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 57321-2024 artfynd.xlsx
+++ b/artfynd/A 57321-2024 artfynd.xlsx
@@ -5837,7 +5837,7 @@
         <v>136091903</v>
       </c>
       <c r="B46" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         <v>136092022</v>
       </c>
       <c r="B47" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -7289,7 +7289,7 @@
         <v>136091964</v>
       </c>
       <c r="B59" t="n">
-        <v>101506</v>
+        <v>101512</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7401,7 +7401,7 @@
         <v>136091947</v>
       </c>
       <c r="B60" t="n">
-        <v>99573</v>
+        <v>99579</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 57321-2024 artfynd.xlsx
+++ b/artfynd/A 57321-2024 artfynd.xlsx
@@ -5837,7 +5837,7 @@
         <v>136091903</v>
       </c>
       <c r="B46" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         <v>136092022</v>
       </c>
       <c r="B47" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -7289,7 +7289,7 @@
         <v>136091964</v>
       </c>
       <c r="B59" t="n">
-        <v>101512</v>
+        <v>101513</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7401,7 +7401,7 @@
         <v>136091947</v>
       </c>
       <c r="B60" t="n">
-        <v>99579</v>
+        <v>99580</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
